--- a/MainTop/12.06.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/12.06.2026 Таня Озон/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\12.06.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54ACEC2-3234-4A35-839B-C419FC2AB7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92529AB-8D01-4BC0-8DFB-20ED00D6BF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -884,7 +884,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -895,6 +895,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1200,22 +1203,11 @@
   <dimension ref="A1:W229"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.140625" customWidth="1"/>
-    <col min="2" max="2" width="3.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.85546875" customWidth="1"/>
-    <col min="4" max="5" width="4.140625" customWidth="1"/>
-    <col min="6" max="6" width="3.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4" customWidth="1"/>
-    <col min="8" max="8" width="4.140625" customWidth="1"/>
-    <col min="9" max="10" width="4.28515625" customWidth="1"/>
-    <col min="11" max="11" width="3.5703125" customWidth="1"/>
-    <col min="12" max="13" width="4.42578125" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" customWidth="1"/>
-    <col min="15" max="15" width="4.140625" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" customWidth="1"/>
-    <col min="17" max="17" width="4" customWidth="1"/>
-    <col min="18" max="18" width="4.7109375" customWidth="1"/>
-    <col min="19" max="19" width="4" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="6" width="5.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" customWidth="1"/>
+    <col min="9" max="19" width="5.42578125" customWidth="1"/>
     <col min="20" max="20" width="9.140625" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="0.140625" customWidth="1"/>
     <col min="22" max="22" width="11.85546875" customWidth="1"/>
@@ -1223,70 +1215,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
